--- a/financial_advisor_forms/012_halal_investment_consultation_booking--financial_advisor_forms.xlsx
+++ b/financial_advisor_forms/012_halal_investment_consultation_booking--financial_advisor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -899,8 +899,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1064,12 +1064,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_11,_'label':_'advisor_1'}</t>
+          <t>advisor_1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 11, 'label': 'Advisor 1'}</t>
+          <t>Advisor 1</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_12,_'label':_'advisor_2'}</t>
+          <t>advisor_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 12, 'label': 'Advisor 2'}</t>
+          <t>Advisor 2</t>
         </is>
       </c>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_13,_'label':_'advisor_3'}</t>
+          <t>advisor_3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 13, 'label': 'Advisor 3'}</t>
+          <t>Advisor 3</t>
         </is>
       </c>
     </row>
@@ -1115,12 +1115,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_14,_'label':_'advisor_4'}</t>
+          <t>advisor_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 14, 'label': 'Advisor 4'}</t>
+          <t>Advisor 4</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_15,_'label':_'advisor_5'}</t>
+          <t>advisor_5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 15, 'label': 'Advisor 5'}</t>
+          <t>Advisor 5</t>
         </is>
       </c>
     </row>
@@ -1149,12 +1149,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_20,_'label':_'email_1'}</t>
+          <t>email_1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 20, 'label': 'Email 1'}</t>
+          <t>Email 1</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_21,_'label':_'email_2'}</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 21, 'label': 'Email 2'}</t>
+          <t>Email 2</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_23,_'label':_'phone_1'}</t>
+          <t>phone_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 23, 'label': 'Phone 1'}</t>
+          <t>Phone 1</t>
         </is>
       </c>
     </row>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_24,_'label':_'phone_2'}</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 24, 'label': 'Phone 2'}</t>
+          <t>Phone 2</t>
         </is>
       </c>
     </row>
